--- a/artfynd/A 28464-2026 artfynd.xlsx
+++ b/artfynd/A 28464-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113888840</v>
+        <v>134665270</v>
       </c>
       <c r="B3" t="n">
-        <v>106229</v>
+        <v>80493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,13 +820,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>778074</v>
+        <v>778026</v>
       </c>
       <c r="R3" t="n">
-        <v>7380200</v>
+        <v>7380209</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150259</v>
+        <v>113888840</v>
       </c>
       <c r="B4" t="n">
         <v>106229</v>
@@ -929,7 +929,7 @@
         <v>778074</v>
       </c>
       <c r="R4" t="n">
-        <v>7380191</v>
+        <v>7380200</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113888837</v>
+        <v>121150259</v>
       </c>
       <c r="B5" t="n">
-        <v>97989</v>
+        <v>106229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777997</v>
+        <v>778074</v>
       </c>
       <c r="R5" t="n">
-        <v>7380250</v>
+        <v>7380191</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119820074</v>
+        <v>113888837</v>
       </c>
       <c r="B6" t="n">
         <v>97989</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>778089</v>
+        <v>777997</v>
       </c>
       <c r="R6" t="n">
-        <v>7380285</v>
+        <v>7380250</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119820080</v>
+        <v>119820074</v>
       </c>
       <c r="B7" t="n">
         <v>97989</v>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>778166</v>
+        <v>778089</v>
       </c>
       <c r="R7" t="n">
-        <v>7380499</v>
+        <v>7380285</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,6 +1308,233 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>119820080</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Randaträsk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>778166</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7380499</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134665066</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98059</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222424</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fjällummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium alpinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Randaträsk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>778089</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7380285</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28464-2026 artfynd.xlsx
+++ b/artfynd/A 28464-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888839</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665270</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888840</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150259</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888837</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820074</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820080</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1535,8 +1575,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665066</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>